--- a/supplementary/Table S1.xlsx
+++ b/supplementary/Table S1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="295">
   <si>
     <t xml:space="preserve">Medicinal Materials</t>
   </si>
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Abbreviation</t>
   </si>
   <si>
-    <t xml:space="preserve">Compound</t>
+    <t xml:space="preserve">Ingredient</t>
   </si>
   <si>
     <t xml:space="preserve">IUPAC Name</t>
@@ -29,10 +29,22 @@
     <t xml:space="preserve">Molecular Formula</t>
   </si>
   <si>
+    <t xml:space="preserve">Molecular Weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMILES</t>
+  </si>
+  <si>
     <t xml:space="preserve">PubChem CID</t>
   </si>
   <si>
-    <t xml:space="preserve">SMILES</t>
+    <t xml:space="preserve">TMMC2 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HERB2 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCMSP ID</t>
   </si>
   <si>
     <t xml:space="preserve">Aconiti Lateralis Radix Praeparata</t>
@@ -41,6 +53,51 @@
     <t xml:space="preserve">ALRP</t>
   </si>
   <si>
+    <t xml:space="preserve">songorine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1R,2R,5R,7R,8R,9R,10R,13R,16S,17R)-11-ethyl-7,16-dihydroxy-13-methyl-6-methylidene-11-azahexacyclo[7.7.2.15,8.01,10.02,8.013,17]nonadecan-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H31NO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]56[C@H]4CC(=O)[C@H](C5)C(=C)[C@H]6O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71456946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">456946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN044335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16β-hydroxycardiopetaline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,6S,8S,9S,13R,16S,17R)-11-ethyl-13-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,6,8,16-tetrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21H33NO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H](C6C[C@@H]4[C@@H]5[C@H]6O)O)O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177826959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN001831</t>
+  </si>
+  <si>
     <t xml:space="preserve">karakolidine</t>
   </si>
   <si>
@@ -50,10 +107,16 @@
     <t xml:space="preserve">C22H35NO5</t>
   </si>
   <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H](C6C[C@@]4([C@@H]5[C@H]6O)O)OC)O)O)C</t>
+  </si>
+  <si>
     <t xml:space="preserve">177825366</t>
   </si>
   <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H](C6C[C@@]4([C@@H]5[C@H]6O)O)OC)O)O)C</t>
+    <t xml:space="preserve">39172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN032091</t>
   </si>
   <si>
     <t xml:space="preserve">chuanfumine</t>
@@ -62,10 +125,244 @@
     <t xml:space="preserve">(1S,2R,5R,6S,7S,8R,9R,10R,13R,16S,17R,18R)-11-ethyl-6-(hydroxymethyl)-13-methyl-11-azahexacyclo[7.7.2.15,8.01,10.02,8.013,17]nonadecane-6,7,16,18-tetrol</t>
   </si>
   <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H]([C@H]31)[C@]56[C@H]4CC[C@H](C5)[C@@]([C@H]6O)(CO)O)O)O)C</t>
+  </si>
+  <si>
     <t xml:space="preserve">177827759</t>
   </si>
   <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H]([C@H]31)[C@]56[C@H]4CC[C@H](C5)[C@@]([C@H]6O)(CO)O)O)O)C</t>
+    <t xml:space="preserve">456947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN020506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isotalatizidine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H37NO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16401028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN031283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-acetylkarakoline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1S,2R,3R,4S,6S,8S,13R,16S,17R)-11-ethyl-8,16-dihydroxy-6-methoxy-13-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H37NO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2CC(C31)[C@]5(C[C@@H](C6C[C@@H]4[C@@H]5[C@H]6OC(=O)C)OC)O)O)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177825823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">465270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">talatisamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">459122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN045433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senbusine B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,7,8,16-tetrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23H37NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1CC2(CCC(C34C2CC(C31)C5(C6C4CC(C6O)C(C5O)OC)O)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">465272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN043686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">senbusine A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16,18-tetrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)O)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20056299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN043684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neoline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,18-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10003218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN036680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002426; MOL004762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chasmanine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25H41NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20055812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN020235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fuziline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4S,5S,6R,7S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,18-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,7,8,16-tetrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@H]([C@@H]6O)[C@H]([C@@H]5O)OC)O)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20056301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN026950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-acetyltalatizamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1S,2R,3R,4S,5R,6S,8S,9S,13S,16S,17R)-11-ethyl-8-hydroxy-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C26H41NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6OC(=O)C)OC)O)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13343321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN001359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hypaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4R,5R,6S,7S,8R,9R,13S,16S,17R,18R)-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8-tetrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123132014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN029815</t>
   </si>
   <si>
     <t xml:space="preserve">mesaconine</t>
@@ -77,130 +374,79 @@
     <t xml:space="preserve">C24H39NO9</t>
   </si>
   <si>
+    <t xml:space="preserve">CN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
     <t xml:space="preserve">122391247</t>
   </si>
   <si>
-    <t xml:space="preserve">CN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">songorine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1R,2R,5R,7R,8R,9R,10R,13R,16S,17R)-11-ethyl-7,16-dihydroxy-13-methyl-6-methylidene-11-azahexacyclo[7.7.2.15,8.01,10.02,8.013,17]nonadecan-4-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C22H31NO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71456946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H]([C@H]31)[C@]56[C@H]4CC(=O)[C@H](C5)C(=C)[C@H]6O)O)C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hypaconine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1S,2R,3R,4R,5R,6S,7S,8R,9R,13S,16S,17R,18R)-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8-tetrol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H39NO8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123132014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fuziline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1S,2R,3R,4S,5S,6R,7S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,18-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,7,8,16-tetrol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H39NO7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20056301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@H]([C@@H]6O)[C@H]([C@@H]5O)OC)O)OC)O)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neoline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,18-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8,16-triol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H39NO6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10003218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)O)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">talatisamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8S,9S,13S,16S,17R)-11-ethyl-6,16-dimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H39NO5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">441761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senbusine B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1R,2S,3S,4S,5S,6R,7S,8R,9S,13S,16S,17R)-11-ethyl-6-methoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-3,4,7,8,16-pentol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C23H37NO7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177825687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5([C@H]([C@@H]([C@H]6C[C@@H]4[C@@]5([C@H]6O)O)OC)O)O)O)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chasmanine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1S,2R,3R,4S,5S,6S,8R,9R,13S,16S,17R,18R)-11-ethyl-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,8-diol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25H41NO6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20055812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@]5(C[C@@H]([C@H]6C[C@@H]4[C@@H]5[C@H]6O)OC)O)OC)OC)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hydroxycardiopetaline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1S,2R,3R,4S,6S,8S,9S,13R,16S,17R)-11-ethyl-13-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,6,8,16-tetrol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C21H33NO4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177826959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2C[C@@H](C31)[C@]5(C[C@@H](C6C[C@@H]4[C@@H]5[C@H]6O)O)O)O)C</t>
+    <t xml:space="preserve">671037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN034774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,2R,3R,4R,5R,6S,7S,8R,9R,13R,14R,16S,17S,18R)-11-ethyl-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25H41NO9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20054813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN014572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">benzoylhypaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1S,2R,3R,4R,5R,6S,7S,8R,9R,13S,16S,17R,18R)-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31H43NO9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123132012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN017819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">benzoyldeoxyaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(1S,2R,3R,4R,5R,6S,7S,8R,9R,13S,16S,17R,18R)-11-ethyl-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C32H45NO9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)COC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21598996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2797</t>
   </si>
   <si>
     <t xml:space="preserve">benzoylmesaconitine</t>
@@ -212,40 +458,16 @@
     <t xml:space="preserve">C31H43NO10</t>
   </si>
   <si>
+    <t xml:space="preserve">CN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
     <t xml:space="preserve">24832659</t>
   </si>
   <si>
-    <t xml:space="preserve">CN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aconine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1S,2R,3R,4R,5R,6S,7S,8R,9R,13R,14R,16S,17S,18R)-11-ethyl-6,16,18-trimethoxy-13-(methoxymethyl)-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25H41NO9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20054813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6O)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14-acetylkarakoline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[(1S,2R,3R,4S,6S,8S,13R,16S,17R)-11-ethyl-8,16-dihydroxy-6-methoxy-13-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] acetate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H37NO5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177825823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2CC(C31)[C@]5(C[C@@H](C6C[C@@H]4[C@@H]5[C@H]6OC(=O)C)OC)O)O)C</t>
+    <t xml:space="preserve">98126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN017823</t>
   </si>
   <si>
     <t xml:space="preserve">benzoylaconine</t>
@@ -257,25 +479,19 @@
     <t xml:space="preserve">C32H45NO10</t>
   </si>
   <si>
+    <t xml:space="preserve">CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
+  </si>
+  <si>
     <t xml:space="preserve">20055771</t>
   </si>
   <si>
-    <t xml:space="preserve">CCN1C[C@@]2([C@@H](C[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)O)COC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">benzoylhypaconine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[(1S,2R,3R,4R,5R,6S,7S,8R,9R,13S,16S,17R,18R)-5,7,8-trihydroxy-6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecan-4-yl] benzoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C31H43NO9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123132012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H](C31)[C@@]5([C@@H]6[C@H]4C[C@@]([C@@H]6OC(=O)C7=CC=CC=C7)([C@H]([C@@H]5O)OC)O)O)OC)OC)COC</t>
+    <t xml:space="preserve">2785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN017811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL002408</t>
   </si>
   <si>
     <t xml:space="preserve">Astragali Radix</t>
@@ -284,6 +500,30 @@
     <t xml:space="preserve">AR</t>
   </si>
   <si>
+    <t xml:space="preserve">formononetin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-hydroxy-3-(4-methoxyphenyl)chromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16H12O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5280378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN026662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL000392; MOL010586</t>
+  </si>
+  <si>
     <t xml:space="preserve">calycosin</t>
   </si>
   <si>
@@ -293,25 +533,124 @@
     <t xml:space="preserve">C16H12O5</t>
   </si>
   <si>
+    <t xml:space="preserve">COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O)O</t>
+  </si>
+  <si>
     <t xml:space="preserve">5280448</t>
   </si>
   <si>
-    <t xml:space="preserve">COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O)O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formononetin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7-hydroxy-3-(4-methoxyphenyl)chromen-4-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16H12O4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5280378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O</t>
+    <t xml:space="preserve">4551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN019425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL000417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-)-methylnissolin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6aR,11aR)-9,10-dimethoxy-6a,11a-dihydro-6H-[1]benzofuro[3,2-c]chromen-3-ol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17H16O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C2=C(C=C1)[C@@H]3COC4=C([C@@H]3O2)C=CC(=C4)O)OC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14077830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN035324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isomucronulatol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-(2-hydroxy-3,4-dimethoxyphenyl)-3,4-dihydro-2H-chromen-7-ol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17H18O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C(=C(C=C1)C2CC3=C(C=C(C=C3)O)OC2)O)OC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">602152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN030954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin-7-O-β-D-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-(4-methoxyphenyl)-7-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxychromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H22O9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">442813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN038168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL000391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin 7-O-β-D-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S,3S,4S,5R,6S)-3,4,5-trihydroxy-6-[3-(4-methoxyphenyl)-4-oxochromen-7-yl]oxyoxane-2-carboxylic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H20O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)C(=O)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71316927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calycosin-7-O-β-D-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-(3-hydroxy-4-methoxyphenyl)-7-[(2S,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxychromen-4-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H22O10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5318267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN008668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL000418; MOL009290</t>
   </si>
   <si>
     <t xml:space="preserve">calycosin-7-O-β-D-glucuronide</t>
@@ -323,28 +662,16 @@
     <t xml:space="preserve">C22H20O11</t>
   </si>
   <si>
+    <t xml:space="preserve">COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)C(=O)O)O)O)O)O</t>
+  </si>
+  <si>
     <t xml:space="preserve">101396032</t>
   </si>
   <si>
-    <t xml:space="preserve">COC1=C(C=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)C(=O)O)O)O)O)O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formononetin 7-O-β-D-glucuronide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2S,3S,4S,5R,6S)-3,4,5-trihydroxy-6-[3-(4-methoxyphenyl)-4-oxochromen-7-yl]oxyoxane-2-carboxylic acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C22H20O10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71316927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COC1=CC=C(C=C1)C2=COC3=C(C2=O)C=CC(=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)C(=O)O)O)O)O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">methylnissolin-3-O-glucoside</t>
+    <t xml:space="preserve">99864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-)-methylinissolin-3-O-β-D-glucoside</t>
   </si>
   <si>
     <t xml:space="preserve">(2S,3R,4S,5S,6R)-2-[[(6aR,11aR)-9,10-dimethoxy-6a,11a-dihydro-6H-[1]benzofuro[3,2-c]chromen-3-yl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
@@ -353,13 +680,19 @@
     <t xml:space="preserve">C23H26O10</t>
   </si>
   <si>
+    <t xml:space="preserve">COC1=C(C2=C(C=C1)[C@@H]3COC4=C([C@@H]3O2)C=CC(=C4)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)CO)O)O)O)OC</t>
+  </si>
+  <si>
     <t xml:space="preserve">101679160</t>
   </si>
   <si>
-    <t xml:space="preserve">COC1=C(C2=C(C=C1)[C@@H]3COC4=C([C@@H]3O2)C=CC(=C4)O[C@H]5[C@@H]([C@H]([C@@H]([C@H](O5)CO)O)O)O)OC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2'-hydroxy-3',4'-dimethoxyisoflavan-7-o-β-d-glucoside</t>
+    <t xml:space="preserve">99406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN013951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isomucronulatol 7-O-glucoside</t>
   </si>
   <si>
     <t xml:space="preserve">(2S,3R,4S,5S,6R)-2-[[(3R)-3-(2-hydroxy-3,4-dimethoxyphenyl)-3,4-dihydro-2H-chromen-7-yl]oxy]-6-(hydroxymethyl)oxane-3,4,5-triol</t>
@@ -368,10 +701,37 @@
     <t xml:space="preserve">C23H28O10</t>
   </si>
   <si>
+    <t xml:space="preserve">COC1=C(C(=C(C=C1)[C@H]2CC3=C(C=C(C=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)OC2)O)OC</t>
+  </si>
+  <si>
     <t xml:space="preserve">15689656</t>
   </si>
   <si>
-    <t xml:space="preserve">COC1=C(C(=C(C=C1)[C@H]2CC3=C(C=C(C=C3)O[C@H]4[C@@H]([C@H]([C@@H]([C@H](O4)CO)O)O)O)OC2)O)OC</t>
+    <t xml:space="preserve">1653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN012323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cycloastragenol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethylpentacyclo[9.7.0.01,3.03,8.012,16]octadecane-6,9,14-triol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30H50O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O)(C)C)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13943286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN022154</t>
   </si>
   <si>
     <t xml:space="preserve">astragaloside IV</t>
@@ -383,10 +743,16 @@
     <t xml:space="preserve">C41H68O14</t>
   </si>
   <si>
+    <t xml:space="preserve">C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)(C)C)O[C@H]8[C@@H]([C@H]([C@@H](CO8)O)O)O</t>
+  </si>
+  <si>
     <t xml:space="preserve">13943297</t>
   </si>
   <si>
-    <t xml:space="preserve">C[C@]12CC[C@@]34C[C@@]35CC[C@@H](C([C@@H]5[C@H](C[C@H]4[C@@]1(C[C@@H]([C@@H]2[C@]6(CC[C@H](O6)C(C)(C)O)C)O)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)(C)C)O[C@H]8[C@@H]([C@H]([C@@H](CO8)O)O)O</t>
+    <t xml:space="preserve">92808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN017222</t>
   </si>
   <si>
     <t xml:space="preserve">astragaloside II</t>
@@ -398,10 +764,100 @@
     <t xml:space="preserve">C43H70O15</t>
   </si>
   <si>
+    <t xml:space="preserve">CC(=O)O[C@@H]1[C@H]([C@@H](CO[C@H]1O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O)O</t>
+  </si>
+  <si>
     <t xml:space="preserve">13996693</t>
   </si>
   <si>
-    <t xml:space="preserve">CC(=O)O[C@@H]1[C@H]([C@@H](CO[C@H]1O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O)O</t>
+    <t xml:space="preserve">306915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN017226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL000403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isoastragaloside II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2S,3R,4S,5R)-3,5-dihydroxy-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-4-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@H]1[C@@H](CO[C@H]([C@@H]1O)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60148655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN030462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">astragaloside I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2S,3R,4S,5R)-3-acetyloxy-5-hydroxy-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-4-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C45H72O16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@H]1[C@@H](CO[C@H]([C@@H]1OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13996685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">346122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN017225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOL000401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isoastragaloside I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(3R,4S,5R,6S)-5-acetyloxy-4-hydroxy-6-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-3-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@@H]1CO[C@H]([C@@H]([C@H]1O)OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60148697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN030461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acetylastragaloside I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(3R,4S,5R,6S)-4,5-diacetyloxy-6-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-15-[(2R,5S)-5-(2-hydroxypropan-2-yl)-2-methyloxolan-2-yl]-7,7,12,16-tetramethyl-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-3-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C47H74O17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@@H]1CO[C@H]([C@@H]([C@H]1OC(=O)C)OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101665834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN014450</t>
   </si>
   <si>
     <t xml:space="preserve">soyasaponin I</t>
@@ -413,10 +869,34 @@
     <t xml:space="preserve">C48H78O18</t>
   </si>
   <si>
+    <t xml:space="preserve">C[C@H]1[C@@H]([C@H]([C@H]([C@@H](O1)O[C@@H]2[C@H]([C@H]([C@H](O[C@H]2O[C@@H]3[C@H]([C@@H]([C@H](O[C@H]3O[C@H]4CC[C@]5([C@H]([C@@]4(C)CO)CC[C@@]6([C@@H]5CC=C7[C@]6(CC[C@@]8([C@H]7CC(C[C@H]8O)(C)C)C)C)C)C)C(=O)O)O)O)CO)O)O)O)O)O</t>
+  </si>
+  <si>
     <t xml:space="preserve">122097</t>
   </si>
   <si>
-    <t xml:space="preserve">C[C@H]1[C@@H]([C@H]([C@H]([C@@H](O1)O[C@@H]2[C@H]([C@H]([C@H](O[C@H]2O[C@@H]3[C@H]([C@@H]([C@H](O[C@H]3O[C@H]4CC[C@]5([C@H]([C@@]4(C)CO)CC[C@@]6([C@@H]5CC=C7[C@]6(CC[C@@]8([C@H]7CC(C[C@H]8O)(C)C)C)C)C)C)C(=O)O)O)O)CO)O)O)O)O)O</t>
+    <t xml:space="preserve">HBIN044433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agroastragaloside III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[(2S,3R,4S,5R)-3-acetyloxy-5-hydroxy-2-[[(1S,3R,6S,8R,9S,11S,12S,14S,15R,16R)-14-hydroxy-7,7,12,16-tetramethyl-15-[(2R,5S)-2-methyl-5-[2-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxypropan-2-yl]oxolan-2-yl]-9-[(2R,3R,4S,5S,6R)-3,4,5-trihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-6-pentacyclo[9.7.0.01,3.03,8.012,16]octadecanyl]oxy]oxan-4-yl] acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C51H82O21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC(=O)O[C@H]1[C@@H](CO[C@H]([C@@H]1OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O[C@H]9[C@@H]([C@H]([C@@H]([C@H](O9)CO)O)O)O)C)C)O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101919088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">919088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBIN014910</t>
   </si>
 </sst>
 </file>
@@ -767,581 +1247,1331 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>357.5</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="F3" t="n">
+        <v>363.5</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
+        <v>393.5</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>393.5</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
+        <v>43</v>
+      </c>
+      <c r="F6" t="n">
+        <v>407.5</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>44</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="F7" t="n">
+        <v>419.6</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
+        <v>57</v>
+      </c>
+      <c r="F8" t="n">
+        <v>421.6</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>58</v>
+      </c>
+      <c r="H8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
+        <v>65</v>
+      </c>
+      <c r="F9" t="n">
+        <v>423.5</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
+        <v>65</v>
+      </c>
+      <c r="F10" t="n">
+        <v>423.5</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
+        <v>80</v>
+      </c>
+      <c r="F11" t="n">
+        <v>437.6</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>81</v>
+      </c>
+      <c r="H11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>451.6</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>89</v>
+      </c>
+      <c r="H12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
+        <v>96</v>
+      </c>
+      <c r="F13" t="n">
+        <v>453.6</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>97</v>
+      </c>
+      <c r="H13" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J13" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" t="s">
-        <v>71</v>
+        <v>104</v>
+      </c>
+      <c r="F14" t="n">
+        <v>463.6</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>105</v>
+      </c>
+      <c r="H14" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" t="s">
-        <v>76</v>
+        <v>112</v>
+      </c>
+      <c r="F15" t="n">
+        <v>469.6</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="H15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" t="s">
-        <v>81</v>
+        <v>119</v>
+      </c>
+      <c r="F16" t="n">
+        <v>485.6</v>
       </c>
       <c r="G16" t="s">
-        <v>82</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" t="s">
+        <v>123</v>
+      </c>
+      <c r="K16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" t="s">
-        <v>86</v>
+        <v>126</v>
+      </c>
+      <c r="F17" t="n">
+        <v>499.6</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="H17" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" t="s">
+        <v>129</v>
+      </c>
+      <c r="J17" t="s">
+        <v>130</v>
+      </c>
+      <c r="K17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" t="s">
-        <v>93</v>
+        <v>133</v>
+      </c>
+      <c r="F18" t="n">
+        <v>573.7</v>
       </c>
       <c r="G18" t="s">
-        <v>94</v>
+        <v>134</v>
+      </c>
+      <c r="H18" t="s">
+        <v>135</v>
+      </c>
+      <c r="I18" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" t="s">
+        <v>137</v>
+      </c>
+      <c r="K18" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" t="s">
-        <v>98</v>
+        <v>141</v>
+      </c>
+      <c r="F19" t="n">
+        <v>587.7</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H19" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" t="s">
+        <v>144</v>
+      </c>
+      <c r="J19"/>
+      <c r="K19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" t="s">
-        <v>103</v>
+        <v>147</v>
+      </c>
+      <c r="F20" t="n">
+        <v>589.7</v>
       </c>
       <c r="G20" t="s">
-        <v>104</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="H20" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" t="s">
+        <v>151</v>
+      </c>
+      <c r="K20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" t="s">
-        <v>108</v>
+        <v>154</v>
+      </c>
+      <c r="F21" t="n">
+        <v>603.7</v>
       </c>
       <c r="G21" t="s">
-        <v>109</v>
+        <v>155</v>
+      </c>
+      <c r="H21" t="s">
+        <v>156</v>
+      </c>
+      <c r="I21" t="s">
+        <v>157</v>
+      </c>
+      <c r="J21" t="s">
+        <v>158</v>
+      </c>
+      <c r="K21" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" t="s">
-        <v>113</v>
+        <v>164</v>
+      </c>
+      <c r="F22" t="n">
+        <v>268.26</v>
       </c>
       <c r="G22" t="s">
-        <v>114</v>
+        <v>165</v>
+      </c>
+      <c r="H22" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22" t="s">
+        <v>167</v>
+      </c>
+      <c r="J22" t="s">
+        <v>168</v>
+      </c>
+      <c r="K22" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="E23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F23" t="s">
-        <v>118</v>
+        <v>172</v>
+      </c>
+      <c r="F23" t="n">
+        <v>284.26</v>
       </c>
       <c r="G23" t="s">
-        <v>119</v>
+        <v>173</v>
+      </c>
+      <c r="H23" t="s">
+        <v>174</v>
+      </c>
+      <c r="I23" t="s">
+        <v>175</v>
+      </c>
+      <c r="J23" t="s">
+        <v>176</v>
+      </c>
+      <c r="K23" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" t="s">
-        <v>123</v>
+        <v>180</v>
+      </c>
+      <c r="F24" t="n">
+        <v>300.3</v>
       </c>
       <c r="G24" t="s">
-        <v>124</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="H24" t="s">
+        <v>182</v>
+      </c>
+      <c r="I24" t="s">
+        <v>183</v>
+      </c>
+      <c r="J24" t="s">
+        <v>184</v>
+      </c>
+      <c r="K24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F25" t="s">
-        <v>128</v>
+        <v>187</v>
+      </c>
+      <c r="F25" t="n">
+        <v>302.32</v>
       </c>
       <c r="G25" t="s">
-        <v>129</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="H25" t="s">
+        <v>189</v>
+      </c>
+      <c r="I25" t="s">
+        <v>190</v>
+      </c>
+      <c r="J25" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="E26" t="s">
-        <v>132</v>
-      </c>
-      <c r="F26" t="s">
-        <v>133</v>
+        <v>194</v>
+      </c>
+      <c r="F26" t="n">
+        <v>430.4</v>
       </c>
       <c r="G26" t="s">
-        <v>134</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="H26" t="s">
+        <v>196</v>
+      </c>
+      <c r="I26" t="s">
+        <v>196</v>
+      </c>
+      <c r="J26" t="s">
+        <v>197</v>
+      </c>
+      <c r="K26" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" t="s">
+        <v>199</v>
+      </c>
+      <c r="D27" t="s">
+        <v>200</v>
+      </c>
+      <c r="E27" t="s">
+        <v>201</v>
+      </c>
+      <c r="F27" t="n">
+        <v>444.4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>202</v>
+      </c>
+      <c r="H27" t="s">
+        <v>203</v>
+      </c>
+      <c r="I27" t="s">
+        <v>204</v>
+      </c>
+      <c r="J27"/>
+      <c r="K27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" t="s">
+        <v>205</v>
+      </c>
+      <c r="D28" t="s">
+        <v>206</v>
+      </c>
+      <c r="E28" t="s">
+        <v>207</v>
+      </c>
+      <c r="F28" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>208</v>
+      </c>
+      <c r="H28" t="s">
+        <v>209</v>
+      </c>
+      <c r="I28" t="s">
+        <v>210</v>
+      </c>
+      <c r="J28" t="s">
+        <v>211</v>
+      </c>
+      <c r="K28" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" t="s">
+        <v>213</v>
+      </c>
+      <c r="D29" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29" t="s">
+        <v>215</v>
+      </c>
+      <c r="F29" t="n">
+        <v>460.4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>216</v>
+      </c>
+      <c r="H29" t="s">
+        <v>217</v>
+      </c>
+      <c r="I29" t="s">
+        <v>218</v>
+      </c>
+      <c r="J29"/>
+      <c r="K29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30" t="n">
+        <v>462.4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>222</v>
+      </c>
+      <c r="H30" t="s">
+        <v>223</v>
+      </c>
+      <c r="I30" t="s">
+        <v>224</v>
+      </c>
+      <c r="J30" t="s">
+        <v>225</v>
+      </c>
+      <c r="K30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" t="s">
+        <v>226</v>
+      </c>
+      <c r="D31" t="s">
+        <v>227</v>
+      </c>
+      <c r="E31" t="s">
+        <v>228</v>
+      </c>
+      <c r="F31" t="n">
+        <v>464.5</v>
+      </c>
+      <c r="G31" t="s">
+        <v>229</v>
+      </c>
+      <c r="H31" t="s">
+        <v>230</v>
+      </c>
+      <c r="I31" t="s">
+        <v>231</v>
+      </c>
+      <c r="J31" t="s">
+        <v>232</v>
+      </c>
+      <c r="K31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>160</v>
+      </c>
+      <c r="B32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" t="s">
+        <v>233</v>
+      </c>
+      <c r="D32" t="s">
+        <v>234</v>
+      </c>
+      <c r="E32" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" t="n">
+        <v>490.7</v>
+      </c>
+      <c r="G32" t="s">
+        <v>236</v>
+      </c>
+      <c r="H32" t="s">
+        <v>237</v>
+      </c>
+      <c r="I32" t="s">
+        <v>238</v>
+      </c>
+      <c r="J32" t="s">
+        <v>239</v>
+      </c>
+      <c r="K32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B33" t="s">
+        <v>161</v>
+      </c>
+      <c r="C33" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E33" t="s">
+        <v>242</v>
+      </c>
+      <c r="F33" t="n">
+        <v>785</v>
+      </c>
+      <c r="G33" t="s">
+        <v>243</v>
+      </c>
+      <c r="H33" t="s">
+        <v>244</v>
+      </c>
+      <c r="I33" t="s">
+        <v>245</v>
+      </c>
+      <c r="J33" t="s">
+        <v>246</v>
+      </c>
+      <c r="K33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" t="s">
+        <v>248</v>
+      </c>
+      <c r="E34" t="s">
+        <v>249</v>
+      </c>
+      <c r="F34" t="n">
+        <v>827</v>
+      </c>
+      <c r="G34" t="s">
+        <v>250</v>
+      </c>
+      <c r="H34" t="s">
+        <v>251</v>
+      </c>
+      <c r="I34" t="s">
+        <v>252</v>
+      </c>
+      <c r="J34" t="s">
+        <v>253</v>
+      </c>
+      <c r="K34" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" t="s">
+        <v>161</v>
+      </c>
+      <c r="C35" t="s">
+        <v>255</v>
+      </c>
+      <c r="D35" t="s">
+        <v>256</v>
+      </c>
+      <c r="E35" t="s">
+        <v>249</v>
+      </c>
+      <c r="F35" t="n">
+        <v>827</v>
+      </c>
+      <c r="G35" t="s">
+        <v>257</v>
+      </c>
+      <c r="H35" t="s">
+        <v>258</v>
+      </c>
+      <c r="I35" t="s">
+        <v>259</v>
+      </c>
+      <c r="J35" t="s">
+        <v>260</v>
+      </c>
+      <c r="K35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" t="s">
+        <v>261</v>
+      </c>
+      <c r="D36" t="s">
+        <v>262</v>
+      </c>
+      <c r="E36" t="s">
+        <v>263</v>
+      </c>
+      <c r="F36" t="n">
+        <v>869</v>
+      </c>
+      <c r="G36" t="s">
+        <v>264</v>
+      </c>
+      <c r="H36" t="s">
+        <v>265</v>
+      </c>
+      <c r="I36" t="s">
+        <v>266</v>
+      </c>
+      <c r="J36" t="s">
+        <v>267</v>
+      </c>
+      <c r="K36" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" t="s">
+        <v>269</v>
+      </c>
+      <c r="D37" t="s">
+        <v>270</v>
+      </c>
+      <c r="E37" t="s">
+        <v>263</v>
+      </c>
+      <c r="F37" t="n">
+        <v>869</v>
+      </c>
+      <c r="G37" t="s">
+        <v>271</v>
+      </c>
+      <c r="H37" t="s">
+        <v>272</v>
+      </c>
+      <c r="I37" t="s">
+        <v>273</v>
+      </c>
+      <c r="J37" t="s">
+        <v>274</v>
+      </c>
+      <c r="K37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" t="s">
+        <v>275</v>
+      </c>
+      <c r="D38" t="s">
+        <v>276</v>
+      </c>
+      <c r="E38" t="s">
+        <v>277</v>
+      </c>
+      <c r="F38" t="n">
+        <v>911.1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>278</v>
+      </c>
+      <c r="H38" t="s">
+        <v>279</v>
+      </c>
+      <c r="I38" t="s">
+        <v>280</v>
+      </c>
+      <c r="J38" t="s">
+        <v>281</v>
+      </c>
+      <c r="K38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>160</v>
+      </c>
+      <c r="B39" t="s">
+        <v>161</v>
+      </c>
+      <c r="C39" t="s">
+        <v>282</v>
+      </c>
+      <c r="D39" t="s">
+        <v>283</v>
+      </c>
+      <c r="E39" t="s">
+        <v>284</v>
+      </c>
+      <c r="F39" t="n">
+        <v>943.1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>285</v>
+      </c>
+      <c r="H39" t="s">
+        <v>286</v>
+      </c>
+      <c r="I39" t="s">
+        <v>286</v>
+      </c>
+      <c r="J39" t="s">
+        <v>287</v>
+      </c>
+      <c r="K39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B40" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" t="s">
+        <v>288</v>
+      </c>
+      <c r="D40" t="s">
+        <v>289</v>
+      </c>
+      <c r="E40" t="s">
+        <v>290</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1031.2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>291</v>
+      </c>
+      <c r="H40" t="s">
+        <v>292</v>
+      </c>
+      <c r="I40" t="s">
+        <v>293</v>
+      </c>
+      <c r="J40" t="s">
+        <v>294</v>
+      </c>
+      <c r="K40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/supplementary/Table S1.xlsx
+++ b/supplementary/Table S1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t xml:space="preserve">Medicinal Materials</t>
   </si>
@@ -26,6 +26,9 @@
     <t xml:space="preserve">PubChem CID</t>
   </si>
   <si>
+    <t xml:space="preserve">InChIKey</t>
+  </si>
+  <si>
     <t xml:space="preserve">Molecular Formula</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
     <t xml:space="preserve">songorine</t>
   </si>
   <si>
+    <t xml:space="preserve">CBOSLVQFGANWTL-DVPYZRQCSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C22H31NO3</t>
   </si>
   <si>
@@ -59,6 +65,9 @@
     <t xml:space="preserve">16β-hydroxycardiopetaline</t>
   </si>
   <si>
+    <t xml:space="preserve">UMENVHXIPMXIRD-CCGCYRHKSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C21H33NO4</t>
   </si>
   <si>
@@ -71,6 +80,9 @@
     <t xml:space="preserve">karakolidine</t>
   </si>
   <si>
+    <t xml:space="preserve">PFSQFYVYGQKXRF-KDNJGJEFSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C22H35NO5</t>
   </si>
   <si>
@@ -83,6 +95,9 @@
     <t xml:space="preserve">chuanfumine</t>
   </si>
   <si>
+    <t xml:space="preserve">FPGSALFSCGNCNM-WUWFTZAFSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCN1C[C@@]2(CC[C@@H]([C@@]34[C@@H]2[C@H]([C@@H]([C@H]31)[C@]56[C@H]4CC[C@H](C5)[C@@]([C@H]6O)(CO)O)O)O)C</t>
   </si>
   <si>
@@ -92,6 +107,9 @@
     <t xml:space="preserve">isotalatizidine</t>
   </si>
   <si>
+    <t xml:space="preserve">RBSZCNOWHDHRFZ-JPAZAREGSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C23H37NO5</t>
   </si>
   <si>
@@ -104,6 +122,9 @@
     <t xml:space="preserve">14-acetylkarakoline</t>
   </si>
   <si>
+    <t xml:space="preserve">JTPMPHWGRDFFAC-YCSUEPHGSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C24H37NO5</t>
   </si>
   <si>
@@ -116,6 +137,9 @@
     <t xml:space="preserve">talatisamine</t>
   </si>
   <si>
+    <t xml:space="preserve">BDCURAWBZJMFIK-FLDLCTCNSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C24H39NO5</t>
   </si>
   <si>
@@ -128,6 +152,9 @@
     <t xml:space="preserve">senbusine A</t>
   </si>
   <si>
+    <t xml:space="preserve">FNRMXORIKJLSGX-LZJIYQGWSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C23H37NO6</t>
   </si>
   <si>
@@ -140,12 +167,18 @@
     <t xml:space="preserve">senbusine B</t>
   </si>
   <si>
+    <t xml:space="preserve">VPFSENNXPMNKNH-UHFFFAOYSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCN1CC2(CCC(C34C2CC(C31)C5(C6C4CC(C6O)C(C5O)OC)O)O)COC</t>
   </si>
   <si>
     <t xml:space="preserve">neoline</t>
   </si>
   <si>
+    <t xml:space="preserve">XRARAKHBJHWUHW-QVUBZLTISA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C24H39NO6</t>
   </si>
   <si>
@@ -158,6 +191,9 @@
     <t xml:space="preserve">chasmanine</t>
   </si>
   <si>
+    <t xml:space="preserve">DBODJJZRZFZBBD-RIVIBFSZSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C25H41NO6</t>
   </si>
   <si>
@@ -170,6 +206,9 @@
     <t xml:space="preserve">fuziline</t>
   </si>
   <si>
+    <t xml:space="preserve">FPECZWKKKKZPPP-KNWHKMNCSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C24H39NO7</t>
   </si>
   <si>
@@ -182,6 +221,9 @@
     <t xml:space="preserve">14-acetyltalatizamine</t>
   </si>
   <si>
+    <t xml:space="preserve">ZHYCSYOPFIUANO-KAJSKAFVSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C26H41NO6</t>
   </si>
   <si>
@@ -194,6 +236,9 @@
     <t xml:space="preserve">hypaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">BQTYHFZQSAKNQU-WIGGLDDKSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C24H39NO8</t>
   </si>
   <si>
@@ -206,6 +251,9 @@
     <t xml:space="preserve">mesaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">GQRPJUIKGLHLLN-VSTHTWNCSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C24H39NO9</t>
   </si>
   <si>
@@ -218,6 +266,9 @@
     <t xml:space="preserve">aconine</t>
   </si>
   <si>
+    <t xml:space="preserve">SQMGCPHFHQGPIF-JIOYIOPFSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C25H41NO9</t>
   </si>
   <si>
@@ -230,6 +281,9 @@
     <t xml:space="preserve">benzoylhypaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">MDFCJNFOINXVSU-SQZQQIIISA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C31H43NO9</t>
   </si>
   <si>
@@ -242,6 +296,9 @@
     <t xml:space="preserve">benzoyldeoxyaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">XZXSGRFMYXBLES-ZDLTZKRLSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C32H45NO9</t>
   </si>
   <si>
@@ -254,6 +311,9 @@
     <t xml:space="preserve">benzoylmesaconitine</t>
   </si>
   <si>
+    <t xml:space="preserve">PULWZCUZNRVAHT-IJNXHYLPSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C31H43NO10</t>
   </si>
   <si>
@@ -266,6 +326,9 @@
     <t xml:space="preserve">benzoylaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">DHJXZSFKLJCHLH-KYSNEVMMSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C32H45NO10</t>
   </si>
   <si>
@@ -284,6 +347,9 @@
     <t xml:space="preserve">formononetin</t>
   </si>
   <si>
+    <t xml:space="preserve">HKQYGTCOTHHOMP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C16H12O4</t>
   </si>
   <si>
@@ -293,6 +359,9 @@
     <t xml:space="preserve">calycosin</t>
   </si>
   <si>
+    <t xml:space="preserve">ZZAJQOPSWWVMBI-UHFFFAOYSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C16H12O5</t>
   </si>
   <si>
@@ -302,6 +371,9 @@
     <t xml:space="preserve">(-)-methylnissolin</t>
   </si>
   <si>
+    <t xml:space="preserve">UOVGCLXUTLXAEC-WFASDCNBSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C17H16O5</t>
   </si>
   <si>
@@ -314,6 +386,9 @@
     <t xml:space="preserve">isomucronulatol</t>
   </si>
   <si>
+    <t xml:space="preserve">NQRBAPDEZYMKFL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C17H18O5</t>
   </si>
   <si>
@@ -323,6 +398,9 @@
     <t xml:space="preserve">formononetin-7-O-β-D-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">MGJLSBDCWOSMHL-MIUGBVLSSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C22H22O9</t>
   </si>
   <si>
@@ -335,6 +413,9 @@
     <t xml:space="preserve">formononetin 7-O-β-D-glucuronide</t>
   </si>
   <si>
+    <t xml:space="preserve">UMBVLOHYPOQARY-SXFAUFNYSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C22H20O10</t>
   </si>
   <si>
@@ -347,6 +428,9 @@
     <t xml:space="preserve">calycosin-7-O-β-D-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">WACBUPFEGWUGPB-MIUGBVLSSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C22H22O10</t>
   </si>
   <si>
@@ -359,6 +443,9 @@
     <t xml:space="preserve">calycosin-7-O-β-D-glucuronide</t>
   </si>
   <si>
+    <t xml:space="preserve">PTHMLNIQOFQYSP-SXFAUFNYSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C22H20O11</t>
   </si>
   <si>
@@ -371,6 +458,9 @@
     <t xml:space="preserve">(-)-methylinissolin-3-O-β-D-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">PCIXSTFFMHVOMF-PBGSHFJYSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C23H26O10</t>
   </si>
   <si>
@@ -383,6 +473,9 @@
     <t xml:space="preserve">isomucronulatol 7-O-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">SXHOGLPTLQBGDO-ZVSSUSCDSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C23H28O10</t>
   </si>
   <si>
@@ -395,6 +488,9 @@
     <t xml:space="preserve">cycloastragenol</t>
   </si>
   <si>
+    <t xml:space="preserve">WENNXORDXYGDTP-UOUCMYEWSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C30H50O5</t>
   </si>
   <si>
@@ -407,6 +503,9 @@
     <t xml:space="preserve">astragaloside IV</t>
   </si>
   <si>
+    <t xml:space="preserve">QMNWISYXSJWHRY-YLNUDOOFSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C41H68O14</t>
   </si>
   <si>
@@ -419,6 +518,9 @@
     <t xml:space="preserve">astragaloside II</t>
   </si>
   <si>
+    <t xml:space="preserve">AYWNHWGQTMCQIV-PENCHUSISA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C43H70O15</t>
   </si>
   <si>
@@ -431,6 +533,9 @@
     <t xml:space="preserve">isoastragaloside II</t>
   </si>
   <si>
+    <t xml:space="preserve">SMZYCXAYGPGYRS-NGTUZWGPSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">CC(=O)O[C@H]1[C@@H](CO[C@H]([C@@H]1O)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C)O</t>
   </si>
   <si>
@@ -440,6 +545,9 @@
     <t xml:space="preserve">astragaloside I</t>
   </si>
   <si>
+    <t xml:space="preserve">KXHCYYSIAXMSPA-OOCCOBHWSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C45H72O16</t>
   </si>
   <si>
@@ -452,6 +560,9 @@
     <t xml:space="preserve">isoastragaloside I</t>
   </si>
   <si>
+    <t xml:space="preserve">HVPKALQHGQMJER-XOUPSZAESA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">CC(=O)O[C@@H]1CO[C@H]([C@@H]([C@H]1O)OC(=O)C)O[C@H]2CC[C@]34C[C@]35CC[C@@]6([C@H]([C@H](C[C@]6([C@@H]5C[C@@H]([C@H]4C2(C)C)O[C@H]7[C@@H]([C@H]([C@@H]([C@H](O7)CO)O)O)O)C)O)[C@]8(CC[C@H](O8)C(C)(C)O)C)C</t>
   </si>
   <si>
@@ -461,6 +572,9 @@
     <t xml:space="preserve">acetylastragaloside I</t>
   </si>
   <si>
+    <t xml:space="preserve">KWZSMZJAHIHRRT-OXLQADOBSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C47H74O17</t>
   </si>
   <si>
@@ -473,6 +587,9 @@
     <t xml:space="preserve">soyasaponin I</t>
   </si>
   <si>
+    <t xml:space="preserve">PTDAHAWQAGSZDD-IOVCITQVSA-N</t>
+  </si>
+  <si>
     <t xml:space="preserve">C48H78O18</t>
   </si>
   <si>
@@ -483,6 +600,9 @@
   </si>
   <si>
     <t xml:space="preserve">agroastragaloside III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOCJNIQHRKBJPF-ZJAHRDLLSA-N</t>
   </si>
   <si>
     <t xml:space="preserve">C51H82O21</t>
@@ -845,1019 +965,1139 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>71456946</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="n">
         <v>357.5</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>177826959</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="n">
         <v>363.5</v>
       </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
         <v>177825366</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="n">
         <v>393.5</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>177827759</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="n">
         <v>393.5</v>
       </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
         <v>16401028</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="n">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="n">
         <v>407.5</v>
       </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="I6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
         <v>177825823</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="n">
         <v>419.6</v>
       </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
         <v>441761</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="n">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="n">
         <v>421.6</v>
       </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>43</v>
+      </c>
+      <c r="I8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
         <v>20056299</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="n">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" t="n">
         <v>423.5</v>
       </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>48</v>
+      </c>
+      <c r="I9" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D10" t="n">
         <v>158049</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" t="n">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="n">
         <v>423.5</v>
       </c>
-      <c r="G10" t="s">
-        <v>42</v>
-      </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>52</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D11" t="n">
         <v>10003218</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" t="n">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="n">
         <v>437.6</v>
       </c>
-      <c r="G11" t="s">
-        <v>45</v>
-      </c>
       <c r="H11" t="s">
-        <v>46</v>
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D12" t="n">
         <v>20055812</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="n">
         <v>451.6</v>
       </c>
-      <c r="G12" t="s">
-        <v>49</v>
-      </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>61</v>
+      </c>
+      <c r="I12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
         <v>20056301</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" t="n">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="n">
         <v>453.6</v>
       </c>
-      <c r="G13" t="s">
-        <v>53</v>
-      </c>
       <c r="H13" t="s">
-        <v>54</v>
+        <v>66</v>
+      </c>
+      <c r="I13" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>13343321</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" t="n">
+        <v>69</v>
+      </c>
+      <c r="F14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" t="n">
         <v>463.6</v>
       </c>
-      <c r="G14" t="s">
-        <v>57</v>
-      </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="I14" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>123132014</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" t="n">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" t="n">
         <v>469.6</v>
       </c>
-      <c r="G15" t="s">
-        <v>61</v>
-      </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D16" t="n">
         <v>122391247</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" t="n">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" t="n">
         <v>485.6</v>
       </c>
-      <c r="G16" t="s">
-        <v>65</v>
-      </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D17" t="n">
         <v>20054813</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" t="n">
+        <v>84</v>
+      </c>
+      <c r="F17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" t="n">
         <v>499.6</v>
       </c>
-      <c r="G17" t="s">
-        <v>69</v>
-      </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>86</v>
+      </c>
+      <c r="I17" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D18" t="n">
         <v>123132012</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" t="n">
+        <v>89</v>
+      </c>
+      <c r="F18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" t="n">
         <v>573.7</v>
       </c>
-      <c r="G18" t="s">
-        <v>73</v>
-      </c>
       <c r="H18" t="s">
-        <v>74</v>
+        <v>91</v>
+      </c>
+      <c r="I18" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D19" t="n">
         <v>21598996</v>
       </c>
       <c r="E19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" t="n">
+        <v>94</v>
+      </c>
+      <c r="F19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" t="n">
         <v>587.7</v>
       </c>
-      <c r="G19" t="s">
-        <v>77</v>
-      </c>
       <c r="H19" t="s">
-        <v>78</v>
+        <v>96</v>
+      </c>
+      <c r="I19" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D20" t="n">
         <v>24832659</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" t="n">
+        <v>99</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" t="n">
         <v>589.7</v>
       </c>
-      <c r="G20" t="s">
-        <v>81</v>
-      </c>
       <c r="H20" t="s">
-        <v>82</v>
+        <v>101</v>
+      </c>
+      <c r="I20" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>20055771</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" t="n">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" t="n">
         <v>603.7</v>
       </c>
-      <c r="G21" t="s">
-        <v>85</v>
-      </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>106</v>
+      </c>
+      <c r="I21" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D22" t="n">
         <v>5280378</v>
       </c>
       <c r="E22" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" t="n">
+        <v>111</v>
+      </c>
+      <c r="F22" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" t="n">
         <v>268.26</v>
       </c>
-      <c r="G22" t="s">
-        <v>91</v>
-      </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>113</v>
+      </c>
+      <c r="I22" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D23" t="n">
         <v>5280448</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
-      </c>
-      <c r="F23" t="n">
+        <v>115</v>
+      </c>
+      <c r="F23" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" t="n">
         <v>284.26</v>
       </c>
-      <c r="G23" t="s">
-        <v>94</v>
-      </c>
       <c r="H23" t="s">
-        <v>94</v>
+        <v>117</v>
+      </c>
+      <c r="I23" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D24" t="n">
         <v>14077830</v>
       </c>
       <c r="E24" t="s">
-        <v>96</v>
-      </c>
-      <c r="F24" t="n">
+        <v>119</v>
+      </c>
+      <c r="F24" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" t="n">
         <v>300.3</v>
       </c>
-      <c r="G24" t="s">
-        <v>97</v>
-      </c>
       <c r="H24" t="s">
-        <v>98</v>
+        <v>121</v>
+      </c>
+      <c r="I24" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D25" t="n">
         <v>602152</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" t="n">
+        <v>124</v>
+      </c>
+      <c r="F25" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" t="n">
         <v>302.32</v>
       </c>
-      <c r="G25" t="s">
-        <v>101</v>
-      </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>126</v>
+      </c>
+      <c r="I25" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="D26" t="n">
         <v>442813</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" t="n">
+        <v>128</v>
+      </c>
+      <c r="F26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" t="n">
         <v>430.4</v>
       </c>
-      <c r="G26" t="s">
-        <v>104</v>
-      </c>
       <c r="H26" t="s">
-        <v>105</v>
+        <v>130</v>
+      </c>
+      <c r="I26" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="D27" t="n">
         <v>71316927</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" t="n">
+        <v>133</v>
+      </c>
+      <c r="F27" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" t="n">
         <v>444.4</v>
       </c>
-      <c r="G27" t="s">
-        <v>108</v>
-      </c>
       <c r="H27" t="s">
-        <v>109</v>
+        <v>135</v>
+      </c>
+      <c r="I27" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="D28" t="n">
         <v>5318267</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" t="n">
+        <v>138</v>
+      </c>
+      <c r="F28" t="s">
+        <v>139</v>
+      </c>
+      <c r="G28" t="n">
         <v>446.4</v>
       </c>
-      <c r="G28" t="s">
-        <v>112</v>
-      </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>140</v>
+      </c>
+      <c r="I28" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="D29" t="n">
         <v>101396032</v>
       </c>
       <c r="E29" t="s">
-        <v>115</v>
-      </c>
-      <c r="F29" t="n">
+        <v>143</v>
+      </c>
+      <c r="F29" t="s">
+        <v>144</v>
+      </c>
+      <c r="G29" t="n">
         <v>460.4</v>
       </c>
-      <c r="G29" t="s">
-        <v>116</v>
-      </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>145</v>
+      </c>
+      <c r="I29" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="D30" t="n">
         <v>101679160</v>
       </c>
       <c r="E30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" t="n">
+        <v>148</v>
+      </c>
+      <c r="F30" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" t="n">
         <v>462.4</v>
       </c>
-      <c r="G30" t="s">
-        <v>120</v>
-      </c>
       <c r="H30" t="s">
-        <v>121</v>
+        <v>150</v>
+      </c>
+      <c r="I30" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="D31" t="n">
         <v>15689656</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" t="n">
+        <v>153</v>
+      </c>
+      <c r="F31" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" t="n">
         <v>464.5</v>
       </c>
-      <c r="G31" t="s">
-        <v>124</v>
-      </c>
       <c r="H31" t="s">
-        <v>125</v>
+        <v>155</v>
+      </c>
+      <c r="I31" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D32" t="n">
         <v>13943286</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" t="n">
+        <v>158</v>
+      </c>
+      <c r="F32" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" t="n">
         <v>490.7</v>
       </c>
-      <c r="G32" t="s">
-        <v>128</v>
-      </c>
       <c r="H32" t="s">
-        <v>129</v>
+        <v>160</v>
+      </c>
+      <c r="I32" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="D33" t="n">
         <v>13943297</v>
       </c>
       <c r="E33" t="s">
-        <v>131</v>
-      </c>
-      <c r="F33" t="n">
+        <v>163</v>
+      </c>
+      <c r="F33" t="s">
+        <v>164</v>
+      </c>
+      <c r="G33" t="n">
         <v>785</v>
       </c>
-      <c r="G33" t="s">
-        <v>132</v>
-      </c>
       <c r="H33" t="s">
-        <v>133</v>
+        <v>165</v>
+      </c>
+      <c r="I33" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="D34" t="n">
         <v>13996693</v>
       </c>
       <c r="E34" t="s">
-        <v>135</v>
-      </c>
-      <c r="F34" t="n">
+        <v>168</v>
+      </c>
+      <c r="F34" t="s">
+        <v>169</v>
+      </c>
+      <c r="G34" t="n">
         <v>827</v>
       </c>
-      <c r="G34" t="s">
-        <v>136</v>
-      </c>
       <c r="H34" t="s">
-        <v>137</v>
+        <v>170</v>
+      </c>
+      <c r="I34" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="D35" t="n">
         <v>60148655</v>
       </c>
       <c r="E35" t="s">
-        <v>135</v>
-      </c>
-      <c r="F35" t="n">
+        <v>173</v>
+      </c>
+      <c r="F35" t="s">
+        <v>169</v>
+      </c>
+      <c r="G35" t="n">
         <v>827</v>
       </c>
-      <c r="G35" t="s">
-        <v>139</v>
-      </c>
       <c r="H35" t="s">
-        <v>140</v>
+        <v>174</v>
+      </c>
+      <c r="I35" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="D36" t="n">
         <v>13996685</v>
       </c>
       <c r="E36" t="s">
-        <v>142</v>
-      </c>
-      <c r="F36" t="n">
+        <v>177</v>
+      </c>
+      <c r="F36" t="s">
+        <v>178</v>
+      </c>
+      <c r="G36" t="n">
         <v>869</v>
       </c>
-      <c r="G36" t="s">
-        <v>143</v>
-      </c>
       <c r="H36" t="s">
-        <v>144</v>
+        <v>179</v>
+      </c>
+      <c r="I36" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="D37" t="n">
         <v>60148697</v>
       </c>
       <c r="E37" t="s">
-        <v>142</v>
-      </c>
-      <c r="F37" t="n">
+        <v>182</v>
+      </c>
+      <c r="F37" t="s">
+        <v>178</v>
+      </c>
+      <c r="G37" t="n">
         <v>869</v>
       </c>
-      <c r="G37" t="s">
-        <v>146</v>
-      </c>
       <c r="H37" t="s">
-        <v>147</v>
+        <v>183</v>
+      </c>
+      <c r="I37" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="D38" t="n">
         <v>101665834</v>
       </c>
       <c r="E38" t="s">
-        <v>149</v>
-      </c>
-      <c r="F38" t="n">
+        <v>186</v>
+      </c>
+      <c r="F38" t="s">
+        <v>187</v>
+      </c>
+      <c r="G38" t="n">
         <v>911.1</v>
       </c>
-      <c r="G38" t="s">
-        <v>150</v>
-      </c>
       <c r="H38" t="s">
-        <v>151</v>
+        <v>188</v>
+      </c>
+      <c r="I38" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="D39" t="n">
         <v>122097</v>
       </c>
       <c r="E39" t="s">
-        <v>153</v>
-      </c>
-      <c r="F39" t="n">
+        <v>191</v>
+      </c>
+      <c r="F39" t="s">
+        <v>192</v>
+      </c>
+      <c r="G39" t="n">
         <v>943.1</v>
       </c>
-      <c r="G39" t="s">
-        <v>154</v>
-      </c>
       <c r="H39" t="s">
-        <v>155</v>
+        <v>193</v>
+      </c>
+      <c r="I39" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="D40" t="n">
         <v>101919088</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
-      </c>
-      <c r="F40" t="n">
+        <v>196</v>
+      </c>
+      <c r="F40" t="s">
+        <v>197</v>
+      </c>
+      <c r="G40" t="n">
         <v>1031.2</v>
       </c>
-      <c r="G40" t="s">
-        <v>158</v>
-      </c>
       <c r="H40" t="s">
-        <v>159</v>
+        <v>198</v>
+      </c>
+      <c r="I40" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
